--- a/assets/forms/cleaning-form-template.xlsx
+++ b/assets/forms/cleaning-form-template.xlsx
@@ -279,7 +279,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +368,19 @@
       <name val="Angsana New"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -975,7 +988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1310,6 +1323,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1769,7 +1788,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" style="2" customWidth="1"/>
@@ -1794,7 +1813,7 @@
       <c r="G1" s="87"/>
       <c r="H1" s="88"/>
     </row>
-    <row r="2" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A2" s="58" t="s">
         <v>59</v>
       </c>
@@ -1805,8 +1824,13 @@
       <c r="F2" s="59"/>
       <c r="G2" s="59"/>
       <c r="H2" s="60"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="J2" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="80" t="s">
         <v>1</v>
       </c>
@@ -1819,8 +1843,13 @@
       </c>
       <c r="G3" s="62"/>
       <c r="H3" s="63"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="J3" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A4" s="82" t="s">
         <v>2</v>
       </c>
@@ -1833,8 +1862,13 @@
       </c>
       <c r="G4" s="65"/>
       <c r="H4" s="66"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="J4" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A5" s="82" t="s">
         <v>4</v>
       </c>
@@ -1847,6 +1881,11 @@
       </c>
       <c r="G5" s="65"/>
       <c r="H5" s="66"/>
+      <c r="J5" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A6" s="84" t="s">
@@ -2577,7 +2616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="2" customWidth="1"/>
@@ -2604,7 +2643,7 @@
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
     </row>
-    <row r="2" spans="1:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="103" t="s">
         <v>1</v>
       </c>
@@ -2623,8 +2662,13 @@
       </c>
       <c r="I2" s="114"/>
       <c r="J2" s="115"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="L2" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="107"/>
       <c r="B3" s="91"/>
       <c r="C3" s="91"/>
@@ -2635,8 +2679,13 @@
       <c r="H3" s="91"/>
       <c r="I3" s="91"/>
       <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="107"/>
       <c r="B4" s="92" t="s">
         <v>64</v>
@@ -2653,8 +2702,13 @@
       </c>
       <c r="I4" s="98"/>
       <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="107"/>
       <c r="B5" s="94"/>
       <c r="C5" s="95"/>
@@ -2665,6 +2719,11 @@
       <c r="H5" s="98"/>
       <c r="I5" s="98"/>
       <c r="J5" s="6"/>
+      <c r="L5" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="107"/>
@@ -3114,7 +3173,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9360BA65-31F0-45A2-85E3-A29E5CA60974}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="2" customWidth="1"/>
@@ -3141,7 +3200,7 @@
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
     </row>
-    <row r="2" spans="1:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="103" t="s">
         <v>1</v>
       </c>
@@ -3160,8 +3219,13 @@
       </c>
       <c r="I2" s="114"/>
       <c r="J2" s="115"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="L2" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="107"/>
       <c r="B3" s="91"/>
       <c r="C3" s="91"/>
@@ -3172,8 +3236,13 @@
       <c r="H3" s="91"/>
       <c r="I3" s="91"/>
       <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="107"/>
       <c r="B4" s="92" t="s">
         <v>64</v>
@@ -3190,8 +3259,13 @@
       </c>
       <c r="I4" s="98"/>
       <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="107"/>
       <c r="B5" s="94"/>
       <c r="C5" s="95"/>
@@ -3202,6 +3276,11 @@
       <c r="H5" s="98"/>
       <c r="I5" s="98"/>
       <c r="J5" s="6"/>
+      <c r="L5" s="120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="107"/>

--- a/assets/forms/cleaning-form-template.xlsx
+++ b/assets/forms/cleaning-form-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Equipment\Air\เอกสารแบบฟอร์มซ่อม ล้าง\ฟอร์ม 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Aircon-manager\assets\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF20A5B-FD62-4D36-968C-8A93D64FC8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3FB299-1AB3-4F4F-A59E-7B3E8A305B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="เอกสารล้าง" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="รูปภาพ_เครื่องที่ 2" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">เอกสารล้าง!$A$1:$H$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'รูปภาพ_เครื่องที่ 1'!$A$1:$J$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'รูปภาพ_เครื่องที่ 2'!$A$1:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">เอกสารล้าง!$A$1:$H$49</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
   <si>
     <t>บันทึกผลการล้างและตรวจสอบเครื่องปรับอากาศ (Node)</t>
   </si>
@@ -273,6 +273,18 @@
   </si>
   <si>
     <t>รูปหลังดำเนินการล้าง</t>
+  </si>
+  <si>
+    <t>วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+  </si>
+  <si>
+    <t>1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+  </si>
+  <si>
+    <t>2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+  </si>
+  <si>
+    <t>3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
   </si>
 </sst>
 </file>
@@ -382,7 +394,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,12 +411,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFEAF0FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -988,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1002,49 +1008,49 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1053,286 +1059,288 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1789,138 +1797,130 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.6328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" style="2" customWidth="1"/>
     <col min="4" max="4" width="10" style="2" customWidth="1"/>
     <col min="5" max="5" width="11" style="2" customWidth="1"/>
-    <col min="6" max="7" width="16.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.625" style="2"/>
+    <col min="6" max="7" width="16.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="28.08984375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="59.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:10" ht="59.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="88"/>
-    </row>
-    <row r="2" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A2" s="58" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="45"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="60"/>
-      <c r="J2" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A3" s="80" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="48"/>
+      <c r="J2" s="37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
       <c r="F3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="62"/>
-      <c r="H3" s="63"/>
-      <c r="J3" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A4" s="82" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
+      <c r="J3" s="38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
       <c r="F4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="65"/>
-      <c r="H4" s="66"/>
-      <c r="J4" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A5" s="82" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+      <c r="J4" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
       <c r="F5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="66"/>
-      <c r="J5" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A6" s="84" t="s">
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+      <c r="J5" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
       <c r="F6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A7" s="58" t="s">
+      <c r="G6" s="55"/>
+      <c r="H6" s="56"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
-    </row>
-    <row r="8" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A8" s="80" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="48"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
       <c r="F8" s="14" t="s">
         <v>9</v>
       </c>
@@ -1929,75 +1929,75 @@
       </c>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="75" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="9"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="75" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="9"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="75" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="77" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A13" s="58" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="60"/>
-    </row>
-    <row r="14" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="48"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="20" t="s">
         <v>17</v>
       </c>
@@ -2011,15 +2011,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
         <v>1</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
@@ -2027,15 +2027,15 @@
       <c r="G15" s="7"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
         <v>2</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="1" t="s">
         <v>22</v>
       </c>
@@ -2043,15 +2043,15 @@
       <c r="G16" s="7"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
         <v>3</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
@@ -2059,15 +2059,15 @@
       <c r="G17" s="7"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
         <v>4</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
       <c r="E18" s="1" t="s">
         <v>22</v>
       </c>
@@ -2075,15 +2075,15 @@
       <c r="G18" s="7"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
         <v>5</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2091,15 +2091,15 @@
       <c r="G19" s="7"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
         <v>6</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
       <c r="E20" s="1" t="s">
         <v>22</v>
       </c>
@@ -2107,15 +2107,15 @@
       <c r="G20" s="7"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
         <v>7</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -2123,15 +2123,15 @@
       <c r="G21" s="7"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
         <v>8</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
       <c r="E22" s="1" t="s">
         <v>22</v>
       </c>
@@ -2139,15 +2139,15 @@
       <c r="G22" s="7"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
         <v>9</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
       <c r="E23" s="1" t="s">
         <v>22</v>
       </c>
@@ -2155,15 +2155,15 @@
       <c r="G23" s="7"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
         <v>10</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="1" t="s">
         <v>32</v>
       </c>
@@ -2171,15 +2171,15 @@
       <c r="G24" s="7"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
         <v>11</v>
       </c>
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="1" t="s">
         <v>34</v>
       </c>
@@ -2187,15 +2187,15 @@
       <c r="G25" s="7"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
         <v>12</v>
       </c>
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="1" t="s">
         <v>36</v>
       </c>
@@ -2203,15 +2203,15 @@
       <c r="G26" s="7"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
         <v>13</v>
       </c>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
       <c r="E27" s="1" t="s">
         <v>38</v>
       </c>
@@ -2219,15 +2219,15 @@
       <c r="G27" s="7"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
         <v>14</v>
       </c>
-      <c r="B28" s="70" t="s">
+      <c r="B28" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
       <c r="E28" s="1" t="s">
         <v>40</v>
       </c>
@@ -2235,15 +2235,15 @@
       <c r="G28" s="7"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
         <v>15</v>
       </c>
-      <c r="B29" s="70" t="s">
+      <c r="B29" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
       <c r="E29" s="1" t="s">
         <v>40</v>
       </c>
@@ -2251,15 +2251,15 @@
       <c r="G29" s="7"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
         <v>16</v>
       </c>
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
       <c r="E30" s="1" t="s">
         <v>42</v>
       </c>
@@ -2267,15 +2267,15 @@
       <c r="G30" s="7"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
         <v>17</v>
       </c>
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
       <c r="E31" s="1" t="s">
         <v>22</v>
       </c>
@@ -2283,15 +2283,15 @@
       <c r="G31" s="7"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
         <v>18</v>
       </c>
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
       <c r="E32" s="1" t="s">
         <v>44</v>
       </c>
@@ -2299,15 +2299,15 @@
       <c r="G32" s="7"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
         <v>19</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
       <c r="E33" s="1" t="s">
         <v>46</v>
       </c>
@@ -2315,15 +2315,15 @@
       <c r="G33" s="7"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
         <v>20</v>
       </c>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="1" t="s">
         <v>22</v>
       </c>
@@ -2331,15 +2331,15 @@
       <c r="G34" s="7"/>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="22">
         <v>21</v>
       </c>
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
       <c r="E35" s="23" t="s">
         <v>22</v>
       </c>
@@ -2347,221 +2347,189 @@
       <c r="G35" s="24"/>
       <c r="H35" s="25"/>
     </row>
-    <row r="36" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A36" s="58" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="59"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="60"/>
-    </row>
-    <row r="37" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A37" s="72" t="s">
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="48"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="73"/>
-      <c r="C37" s="73"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
       <c r="D37" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="57"/>
-    </row>
-    <row r="38" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A38" s="53" t="s">
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="72"/>
+      <c r="H37" s="73"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
       <c r="D38" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
       <c r="G38" s="5"/>
       <c r="H38" s="6"/>
     </row>
-    <row r="39" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A39" s="58" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="60"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="61"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="63"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="64"/>
-      <c r="B41" s="65"/>
-      <c r="C41" s="65"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="66"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="64"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="66"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="67"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="69"/>
-    </row>
-    <row r="44" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A44" s="58" t="s">
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="74"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="52"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="63"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="42"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="63"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="42"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="64"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="56"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="59"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="60"/>
-    </row>
-    <row r="45" spans="1:8" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="32" t="s">
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+    </row>
+    <row r="45" spans="1:8" ht="16.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="35" t="s">
+      <c r="B45" s="79"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="80"/>
+      <c r="F45" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="G45" s="33"/>
-      <c r="H45" s="36"/>
-    </row>
-    <row r="46" spans="1:8" s="28" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="37" t="s">
+      <c r="G45" s="79"/>
+      <c r="H45" s="82"/>
+    </row>
+    <row r="46" spans="1:8" s="28" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="40" t="s">
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
+      <c r="D46" s="84"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="G46" s="38"/>
-      <c r="H46" s="41"/>
-    </row>
-    <row r="47" spans="1:8" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="42" t="s">
+      <c r="G46" s="84"/>
+      <c r="H46" s="87"/>
+    </row>
+    <row r="47" spans="1:8" ht="16.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="43"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="45" t="s">
+      <c r="B47" s="89"/>
+      <c r="C47" s="89"/>
+      <c r="D47" s="89"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G47" s="43"/>
-      <c r="H47" s="46"/>
-    </row>
-    <row r="48" spans="1:8" s="28" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="47" t="s">
+      <c r="G47" s="89"/>
+      <c r="H47" s="92"/>
+    </row>
+    <row r="48" spans="1:8" s="28" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="50" t="s">
+      <c r="B48" s="94"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="94"/>
+      <c r="E48" s="95"/>
+      <c r="F48" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="G48" s="51"/>
-      <c r="H48" s="52"/>
-    </row>
-    <row r="49" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="29" t="s">
+      <c r="G48" s="97"/>
+      <c r="H48" s="98"/>
+    </row>
+    <row r="49" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="31"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A44:H44"/>
@@ -2576,15 +2544,47 @@
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:F38 G37:H37">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
@@ -2617,223 +2617,215 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.625" style="2" customWidth="1"/>
-    <col min="5" max="6" width="12.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="2.625" style="2" customWidth="1"/>
-    <col min="8" max="9" width="12.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" style="2"/>
+    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="12.6328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6328125" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="2.6328125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="12.6328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="2.6328125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="100" t="s">
+    <row r="1" spans="1:12" ht="56.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="102"/>
-    </row>
-    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="103" t="s">
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="104"/>
+    </row>
+    <row r="2" spans="1:12" ht="21.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="113" t="s">
+      <c r="B2" s="106"/>
+      <c r="C2" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="105" t="s">
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="106"/>
-      <c r="H2" s="113" t="s">
+      <c r="G2" s="108"/>
+      <c r="H2" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="114"/>
-      <c r="J2" s="115"/>
-      <c r="L2" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A3" s="107"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="111"/>
+      <c r="L2" s="37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="31"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="6"/>
-      <c r="L3" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="107"/>
-      <c r="B4" s="92" t="s">
+      <c r="L3" s="38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="31"/>
+      <c r="B4" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="98" t="s">
+      <c r="C4" s="114"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="98"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="98" t="s">
+      <c r="H4" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="98"/>
+      <c r="I4" s="112"/>
       <c r="J4" s="6"/>
-      <c r="L4" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="107"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
+      <c r="L4" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="31"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
       <c r="J5" s="6"/>
-      <c r="L5" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="107"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
+      <c r="L5" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="31"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="107"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
+    <row r="7" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="31"/>
+      <c r="B7" s="115"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="107"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
+    <row r="8" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="31"/>
+      <c r="B8" s="115"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="107"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="108" t="s">
+    <row r="9" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="31"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="107"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="31"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="107"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="31"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="107"/>
-      <c r="B12" s="96"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
+    <row r="12" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="31"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="107"/>
-      <c r="B13" s="116" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="31"/>
+      <c r="B13" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="118" t="s">
+      <c r="C13" s="100"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="118"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="118" t="s">
+      <c r="F13" s="101"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="118"/>
+      <c r="I13" s="101"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="107"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="31"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="121"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -2841,302 +2833,309 @@
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="107"/>
-      <c r="B15" s="92" t="s">
+    <row r="15" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="31"/>
+      <c r="B15" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="93"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="98" t="s">
+      <c r="C15" s="114"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="98"/>
+      <c r="F15" s="112"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="98" t="s">
+      <c r="H15" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="98"/>
+      <c r="I15" s="112"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="107"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
+    <row r="16" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="31"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A17" s="107"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="31"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="107"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
+    <row r="18" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="31"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="107"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
+    <row r="19" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="31"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="107"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="108" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="31"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="107"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
+    <row r="21" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="31"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="107"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
+    <row r="22" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="31"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="107"/>
-      <c r="B23" s="96"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="31"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="107"/>
-      <c r="B24" s="116" t="s">
+    <row r="24" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="31"/>
+      <c r="B24" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="118" t="s">
+      <c r="C24" s="100"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="118"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="118" t="s">
+      <c r="F24" s="101"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="118"/>
+      <c r="I24" s="101"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="107"/>
-      <c r="B25" s="99"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="109" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="31"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A26" s="107"/>
-      <c r="B26" s="92" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="31"/>
+      <c r="B26" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="93"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="98" t="s">
+      <c r="C26" s="114"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="98"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="98" t="s">
+      <c r="H26" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I26" s="98"/>
+      <c r="I26" s="112"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="107"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
+    <row r="27" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="31"/>
+      <c r="B27" s="115"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="107"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
+    <row r="28" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="31"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="98"/>
-      <c r="I28" s="98"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A29" s="107"/>
-      <c r="B29" s="94"/>
-      <c r="C29" s="95"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="31"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A30" s="107"/>
-      <c r="B30" s="94"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="31"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="98"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="112"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="107"/>
-      <c r="B31" s="94"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="108" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="31"/>
+      <c r="B31" s="115"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="107"/>
-      <c r="B32" s="94"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="31"/>
+      <c r="B32" s="115"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="112"/>
+      <c r="I32" s="112"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="107"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="31"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="107"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="31"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="112"/>
+      <c r="I34" s="112"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="107"/>
-      <c r="B35" s="116" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="31"/>
+      <c r="B35" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="117"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="118" t="s">
+      <c r="C35" s="100"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="118"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="118" t="s">
+      <c r="F35" s="101"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="I35" s="118"/>
+      <c r="I35" s="101"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="110"/>
-      <c r="B36" s="111"/>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="112"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="34"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H15:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B26:C34"/>
+    <mergeCell ref="E26:F34"/>
+    <mergeCell ref="H26:I34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="H35:I35"/>
@@ -3153,13 +3152,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B15:C23"/>
     <mergeCell ref="E15:F23"/>
-    <mergeCell ref="H15:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B26:C34"/>
-    <mergeCell ref="E26:F34"/>
-    <mergeCell ref="H26:I34"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.51181102362204722" bottom="0.31496062992125984" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3174,223 +3166,215 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9360BA65-31F0-45A2-85E3-A29E5CA60974}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.625" style="2" customWidth="1"/>
-    <col min="5" max="6" width="12.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="2.625" style="2" customWidth="1"/>
-    <col min="8" max="9" width="12.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" style="2"/>
+    <col min="1" max="1" width="2.6328125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="12.6328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6328125" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="2.6328125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="12.6328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="2.6328125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="100" t="s">
+    <row r="1" spans="1:12" ht="56.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="102"/>
-    </row>
-    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="103" t="s">
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="104"/>
+    </row>
+    <row r="2" spans="1:12" ht="21.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="113" t="s">
+      <c r="B2" s="106"/>
+      <c r="C2" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="105" t="s">
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="106"/>
-      <c r="H2" s="113" t="s">
+      <c r="G2" s="108"/>
+      <c r="H2" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="114"/>
-      <c r="J2" s="115"/>
-      <c r="L2" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A3" s="107"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="111"/>
+      <c r="L2" s="37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="31"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="6"/>
-      <c r="L3" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="107"/>
-      <c r="B4" s="92" t="s">
+      <c r="L3" s="38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="31"/>
+      <c r="B4" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="98" t="s">
+      <c r="C4" s="114"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="98"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="98" t="s">
+      <c r="H4" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="98"/>
+      <c r="I4" s="112"/>
       <c r="J4" s="6"/>
-      <c r="L4" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="107"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
+      <c r="L4" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="31"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
       <c r="J5" s="6"/>
-      <c r="L5" s="120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="107"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
+      <c r="L5" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="31"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="107"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
+    <row r="7" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="31"/>
+      <c r="B7" s="115"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="107"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
+    <row r="8" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="31"/>
+      <c r="B8" s="115"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="107"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="108" t="s">
+    <row r="9" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="31"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="107"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="31"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="107"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="31"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="107"/>
-      <c r="B12" s="96"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
+    <row r="12" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="31"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="107"/>
-      <c r="B13" s="116" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="31"/>
+      <c r="B13" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="118" t="s">
+      <c r="C13" s="100"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="118"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="118" t="s">
+      <c r="F13" s="101"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="118"/>
+      <c r="I13" s="101"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="107"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="31"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="121"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -3398,302 +3382,316 @@
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="107"/>
-      <c r="B15" s="92" t="s">
+    <row r="15" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="31"/>
+      <c r="B15" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="93"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="98" t="s">
+      <c r="C15" s="114"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="98"/>
+      <c r="F15" s="112"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="98" t="s">
+      <c r="H15" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="98"/>
+      <c r="I15" s="112"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="107"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
+    <row r="16" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="31"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A17" s="107"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="31"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="107"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
+    <row r="18" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="31"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="107"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
+    <row r="19" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="31"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="107"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="108" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="31"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="107"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
+    <row r="21" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="31"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="107"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
+    <row r="22" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="31"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="107"/>
-      <c r="B23" s="96"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="31"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="107"/>
-      <c r="B24" s="116" t="s">
+    <row r="24" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="31"/>
+      <c r="B24" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="118" t="s">
+      <c r="C24" s="100"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="118"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="118" t="s">
+      <c r="F24" s="101"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="118"/>
+      <c r="I24" s="101"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="107"/>
-      <c r="B25" s="99"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="109" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="31"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A26" s="107"/>
-      <c r="B26" s="92" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="31"/>
+      <c r="B26" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="93"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="98" t="s">
+      <c r="C26" s="114"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="98"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="98" t="s">
+      <c r="H26" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I26" s="98"/>
+      <c r="I26" s="112"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="107"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
+    <row r="27" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="31"/>
+      <c r="B27" s="115"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="98"/>
-      <c r="I27" s="98"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="107"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
+    <row r="28" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="31"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="98"/>
-      <c r="I28" s="98"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A29" s="107"/>
-      <c r="B29" s="94"/>
-      <c r="C29" s="95"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="31"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A30" s="107"/>
-      <c r="B30" s="94"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="31"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="98"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="112"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="107"/>
-      <c r="B31" s="94"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="108" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="31"/>
+      <c r="B31" s="115"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="107"/>
-      <c r="B32" s="94"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="31"/>
+      <c r="B32" s="115"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="112"/>
+      <c r="I32" s="112"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="107"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="95"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="31"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="107"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="31"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="112"/>
+      <c r="I34" s="112"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="107"/>
-      <c r="B35" s="116" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="31"/>
+      <c r="B35" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="117"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="118" t="s">
+      <c r="C35" s="100"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="118"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="118" t="s">
+      <c r="F35" s="101"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="I35" s="118"/>
+      <c r="I35" s="101"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="110"/>
-      <c r="B36" s="111"/>
-      <c r="C36" s="111"/>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="112"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="34"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B4:C12"/>
+    <mergeCell ref="E4:F12"/>
+    <mergeCell ref="H4:I12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B15:C23"/>
+    <mergeCell ref="E15:F23"/>
+    <mergeCell ref="H15:I23"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="H35:I35"/>
@@ -3703,20 +3701,6 @@
     <mergeCell ref="B26:C34"/>
     <mergeCell ref="E26:F34"/>
     <mergeCell ref="H26:I34"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B15:C23"/>
-    <mergeCell ref="E15:F23"/>
-    <mergeCell ref="H15:I23"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B4:C12"/>
-    <mergeCell ref="E4:F12"/>
-    <mergeCell ref="H4:I12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.51181102362204722" bottom="0.31496062992125984" header="0.51181102362204722" footer="0.51181102362204722"/>
